--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_master_info.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_master_info.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\天使之战\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
@@ -2748,7 +2753,7 @@
     <t>攻击力强化</t>
   </si>
   <si>
-    <t>200011#3|200021#3</t>
+    <t>200041#3</t>
   </si>
   <si>
     <t>攻击力增加3</t>
@@ -2757,7 +2762,7 @@
     <t>21202</t>
   </si>
   <si>
-    <t>200011#6|200021#6</t>
+    <t>200041#6</t>
   </si>
   <si>
     <t>攻击力增加6</t>
@@ -2766,7 +2771,7 @@
     <t>21203</t>
   </si>
   <si>
-    <t>200011#9|200021#9</t>
+    <t>200041#9</t>
   </si>
   <si>
     <t>攻击力增加9</t>
@@ -2775,7 +2780,7 @@
     <t>21204</t>
   </si>
   <si>
-    <t>200011#12|200021#12</t>
+    <t>200041#12</t>
   </si>
   <si>
     <t>攻击力增加12</t>
@@ -2784,7 +2789,7 @@
     <t>21205</t>
   </si>
   <si>
-    <t>200011#15|200021#15</t>
+    <t>200041#15</t>
   </si>
   <si>
     <t>攻击力增加15</t>
@@ -2793,7 +2798,7 @@
     <t>21206</t>
   </si>
   <si>
-    <t>200011#18|200021#18</t>
+    <t>200041#18</t>
   </si>
   <si>
     <t>攻击力增加18</t>
@@ -2802,7 +2807,7 @@
     <t>21207</t>
   </si>
   <si>
-    <t>200011#21|200021#21</t>
+    <t>200041#21</t>
   </si>
   <si>
     <t>攻击力增加21</t>
@@ -2811,7 +2816,7 @@
     <t>21208</t>
   </si>
   <si>
-    <t>200011#24|200021#24</t>
+    <t>200041#24</t>
   </si>
   <si>
     <t>攻击力增加24</t>
@@ -2820,7 +2825,7 @@
     <t>21209</t>
   </si>
   <si>
-    <t>200011#27|200021#27</t>
+    <t>200041#27</t>
   </si>
   <si>
     <t>攻击力增加27</t>
@@ -2829,7 +2834,7 @@
     <t>21210</t>
   </si>
   <si>
-    <t>200011#30|200021#30</t>
+    <t>200041#30</t>
   </si>
   <si>
     <t>攻击力增加30</t>
@@ -2838,7 +2843,7 @@
     <t>21211</t>
   </si>
   <si>
-    <t>200011#33|200021#33</t>
+    <t>200041#33</t>
   </si>
   <si>
     <t>攻击力增加33</t>
@@ -2847,7 +2852,7 @@
     <t>21212</t>
   </si>
   <si>
-    <t>200011#36|200021#36</t>
+    <t>200041#36</t>
   </si>
   <si>
     <t>攻击力增加36</t>
@@ -2856,7 +2861,7 @@
     <t>21213</t>
   </si>
   <si>
-    <t>200011#39|200021#39</t>
+    <t>200041#39</t>
   </si>
   <si>
     <t>攻击力增加39</t>
@@ -2865,7 +2870,7 @@
     <t>21214</t>
   </si>
   <si>
-    <t>200011#42|200021#42</t>
+    <t>200041#42</t>
   </si>
   <si>
     <t>攻击力增加42</t>
@@ -2874,7 +2879,7 @@
     <t>21215</t>
   </si>
   <si>
-    <t>200011#45|200021#45</t>
+    <t>200041#45</t>
   </si>
   <si>
     <t>攻击力增加45</t>
@@ -2883,7 +2888,7 @@
     <t>21216</t>
   </si>
   <si>
-    <t>200011#48|200021#48</t>
+    <t>200041#48</t>
   </si>
   <si>
     <t>攻击力增加48</t>
@@ -2892,7 +2897,7 @@
     <t>21217</t>
   </si>
   <si>
-    <t>200011#51|200021#51</t>
+    <t>200041#51</t>
   </si>
   <si>
     <t>攻击力增加51</t>
@@ -2901,7 +2906,7 @@
     <t>21218</t>
   </si>
   <si>
-    <t>200011#54|200021#54</t>
+    <t>200041#54</t>
   </si>
   <si>
     <t>攻击力增加54</t>
@@ -2910,7 +2915,7 @@
     <t>21219</t>
   </si>
   <si>
-    <t>200011#57|200021#57</t>
+    <t>200041#57</t>
   </si>
   <si>
     <t>攻击力增加57</t>
@@ -2919,7 +2924,7 @@
     <t>21220</t>
   </si>
   <si>
-    <t>200011#60|200021#60</t>
+    <t>200041#60</t>
   </si>
   <si>
     <t>攻击力增加60</t>
